--- a/Windows_Ransomware_Intrusion/evidence/PrefetchFiles/PYTHON.EXE-E2B2C5E6.xlsx
+++ b/Windows_Ransomware_Intrusion/evidence/PrefetchFiles/PYTHON.EXE-E2B2C5E6.xlsx
@@ -1,25 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emma\Desktop\Parsed\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emma/DFIR-Simulation-Platform/Windows_Ransomware_Intrusion/evidence/PrefetchFiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02C35151-8112-4EBA-842B-6595B0BEEAD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36BECF2A-466A-154F-B3E7-0C6CBF76BF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7116" yWindow="1236" windowWidth="15024" windowHeight="11064" xr2:uid="{F43FE836-AC3E-48EE-8EC6-973C1E1DF6FF}"/>
+    <workbookView xWindow="0" yWindow="1240" windowWidth="22140" windowHeight="11020" xr2:uid="{F43FE836-AC3E-48EE-8EC6-973C1E1DF6FF}"/>
   </bookViews>
   <sheets>
     <sheet name="PYTHON.EXE-E2B2C5E6" sheetId="2" r:id="rId1"/>
     <sheet name="PYTHON.EXE-E2B2C5E6_Timeline" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_1" localSheetId="0" hidden="1">'PYTHON.EXE-E2B2C5E6'!$A$1:$AA$2</definedName>
-    <definedName name="ExternalData_1" localSheetId="1" hidden="1">'PYTHON.EXE-E2B2C5E6_Timeline'!$A$1:$B$9</definedName>
-    <definedName name="ExternalData_1" localSheetId="1" hidden="1">'PYTHON.EXE-E2B2C5E6_Timeline'!$A$1:$B$9</definedName>
+    <definedName name="ExternalData_1" localSheetId="0" hidden="1">'PYTHON.EXE-E2B2C5E6'!$A$1:$V$2</definedName>
+    <definedName name="ExternalData_1" localSheetId="1" hidden="1">'PYTHON.EXE-E2B2C5E6_Timeline'!$A$1:$B$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -56,22 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
-  <si>
-    <t>Note</t>
-  </si>
-  <si>
-    <t>SourceFilename</t>
-  </si>
-  <si>
-    <t>SourceCreated</t>
-  </si>
-  <si>
-    <t>SourceModified</t>
-  </si>
-  <si>
-    <t>SourceAccessed</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="32">
   <si>
     <t>ExecutableName</t>
   </si>
@@ -140,9 +124,6 @@
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>C:\Users\Emma\Desktop\evidence\System\PYTHON.EXE-E2B2C5E6.pf</t>
   </si>
   <si>
     <t>PYTHON.EXE</t>
@@ -212,78 +193,63 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="26">
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
+  <dxfs count="21">
+    <dxf>
+      <numFmt numFmtId="27" formatCode="m/d/yy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="m/d/yy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="m/d/yy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="m/d/yy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="m/d/yy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="m/d/yy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="m/d/yy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -307,12 +273,7 @@
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="1" xr16:uid="{32430D21-5EB5-476F-9AF4-E2241E68E1AF}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
   <queryTableRefresh nextId="28">
-    <queryTableFields count="27">
-      <queryTableField id="1" name="Note" tableColumnId="1"/>
-      <queryTableField id="2" name="SourceFilename" tableColumnId="2"/>
-      <queryTableField id="3" name="SourceCreated" tableColumnId="3"/>
-      <queryTableField id="4" name="SourceModified" tableColumnId="4"/>
-      <queryTableField id="5" name="SourceAccessed" tableColumnId="5"/>
+    <queryTableFields count="22">
       <queryTableField id="6" name="ExecutableName" tableColumnId="6"/>
       <queryTableField id="7" name="Hash" tableColumnId="7"/>
       <queryTableField id="8" name="Size" tableColumnId="8"/>
@@ -336,6 +297,13 @@
       <queryTableField id="26" name="FilesLoaded" tableColumnId="26"/>
       <queryTableField id="27" name="ParsingError" tableColumnId="27"/>
     </queryTableFields>
+    <queryTableDeletedFields count="5">
+      <deletedField name="Note"/>
+      <deletedField name="SourceFilename"/>
+      <deletedField name="SourceCreated"/>
+      <deletedField name="SourceModified"/>
+      <deletedField name="SourceAccessed"/>
+    </queryTableDeletedFields>
   </queryTableRefresh>
 </queryTable>
 </file>
@@ -352,35 +320,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EA44C9CE-E850-47A4-A59F-51D28BD095BE}" name="_20260429005736_PECmd_Output" displayName="_20260429005736_PECmd_Output" ref="A1:AA2" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:AA2" xr:uid="{EA44C9CE-E850-47A4-A59F-51D28BD095BE}"/>
-  <tableColumns count="27">
-    <tableColumn id="1" xr3:uid="{5603B2EC-23C4-4CA9-83F7-D5544330FA21}" uniqueName="1" name="Note" queryTableFieldId="1" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{7E9F730D-59B3-4779-A792-0412A0B3CD4B}" uniqueName="2" name="SourceFilename" queryTableFieldId="2" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{30AB8C9C-4207-47AB-A2E5-0FAADBB4CC0D}" uniqueName="3" name="SourceCreated" queryTableFieldId="3" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{75F80106-79C2-4E82-9EC4-DE65A0E75BE0}" uniqueName="4" name="SourceModified" queryTableFieldId="4" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{0F5C6A3A-D616-4A64-86A2-D9E7A0BEAD71}" uniqueName="5" name="SourceAccessed" queryTableFieldId="5" dataDxfId="21"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EA44C9CE-E850-47A4-A59F-51D28BD095BE}" name="_20260429005736_PECmd_Output" displayName="_20260429005736_PECmd_Output" ref="A1:V2" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:V2" xr:uid="{EA44C9CE-E850-47A4-A59F-51D28BD095BE}"/>
+  <tableColumns count="22">
     <tableColumn id="6" xr3:uid="{1AB9CD27-0598-4986-B19B-9ED1CA0DBEEE}" uniqueName="6" name="ExecutableName" queryTableFieldId="6" dataDxfId="20"/>
     <tableColumn id="7" xr3:uid="{465E4570-E3BD-4917-A3C6-EBFD4B9D21A6}" uniqueName="7" name="Hash" queryTableFieldId="7" dataDxfId="19"/>
     <tableColumn id="8" xr3:uid="{273D2B4E-CB2A-407D-90F9-6946001BCFB0}" uniqueName="8" name="Size" queryTableFieldId="8"/>
     <tableColumn id="9" xr3:uid="{D3ECD9EE-9C8D-4931-B8BD-0BB41D38D0B4}" uniqueName="9" name="Version" queryTableFieldId="9" dataDxfId="18"/>
     <tableColumn id="10" xr3:uid="{11A6FFF9-BECF-4FC7-BE67-7CB4510849AE}" uniqueName="10" name="RunCount" queryTableFieldId="10"/>
     <tableColumn id="11" xr3:uid="{318366D6-DCC8-4B24-BBCD-8A7C6D754553}" uniqueName="11" name="LastRun" queryTableFieldId="11" dataDxfId="17"/>
-    <tableColumn id="12" xr3:uid="{2880BD60-09A2-4D7E-9B3F-885D02542C20}" uniqueName="12" name="PreviousRun0" queryTableFieldId="12" dataDxfId="16"/>
-    <tableColumn id="13" xr3:uid="{E3E8CC1C-2048-4C68-8C73-9C23BAF8E279}" uniqueName="13" name="PreviousRun1" queryTableFieldId="13" dataDxfId="15"/>
-    <tableColumn id="14" xr3:uid="{AE7BAA4D-E3D2-4285-BE3D-A239D2F62EF4}" uniqueName="14" name="PreviousRun2" queryTableFieldId="14" dataDxfId="14"/>
-    <tableColumn id="15" xr3:uid="{301D8E6F-5DBC-42B5-8017-5B59010563CF}" uniqueName="15" name="PreviousRun3" queryTableFieldId="15" dataDxfId="13"/>
-    <tableColumn id="16" xr3:uid="{D035B195-9C84-45C1-B235-F06BB2F9A3DF}" uniqueName="16" name="PreviousRun4" queryTableFieldId="16" dataDxfId="12"/>
-    <tableColumn id="17" xr3:uid="{7D5B7342-1370-4300-B6E6-1A36CD80694B}" uniqueName="17" name="PreviousRun5" queryTableFieldId="17" dataDxfId="11"/>
-    <tableColumn id="18" xr3:uid="{A389CD95-6B82-4DB3-AED0-52BE817E75F0}" uniqueName="18" name="PreviousRun6" queryTableFieldId="18" dataDxfId="10"/>
-    <tableColumn id="19" xr3:uid="{9B99B349-B48C-49EC-883C-00BE7E54D37D}" uniqueName="19" name="Volume0Name" queryTableFieldId="19" dataDxfId="9"/>
-    <tableColumn id="20" xr3:uid="{DA95DC40-6B11-4BC8-A7FC-48424A1DF5ED}" uniqueName="20" name="Volume0Serial" queryTableFieldId="20" dataDxfId="8"/>
-    <tableColumn id="21" xr3:uid="{6905E521-84A5-4DEA-A4D9-9767759B6F0F}" uniqueName="21" name="Volume0Created" queryTableFieldId="21" dataDxfId="7"/>
-    <tableColumn id="22" xr3:uid="{BC82989A-24DF-4EDB-80D2-024D565C2C30}" uniqueName="22" name="Volume1Name" queryTableFieldId="22" dataDxfId="6"/>
-    <tableColumn id="23" xr3:uid="{1EF047D8-22C4-40DB-A5C8-16C025AC50EF}" uniqueName="23" name="Volume1Serial" queryTableFieldId="23" dataDxfId="5"/>
-    <tableColumn id="24" xr3:uid="{BDC1B3CA-3F53-4B10-8636-BFE8CAEDDD90}" uniqueName="24" name="Volume1Created" queryTableFieldId="24" dataDxfId="4"/>
-    <tableColumn id="25" xr3:uid="{02AC2FC1-9EAF-49E2-97EB-698A7B7C06C4}" uniqueName="25" name="Directories" queryTableFieldId="25" dataDxfId="3"/>
-    <tableColumn id="26" xr3:uid="{E668B0CD-9181-44EB-8C2E-BC0D72847997}" uniqueName="26" name="FilesLoaded" queryTableFieldId="26" dataDxfId="2"/>
+    <tableColumn id="12" xr3:uid="{2880BD60-09A2-4D7E-9B3F-885D02542C20}" uniqueName="12" name="PreviousRun0" queryTableFieldId="12" dataDxfId="5"/>
+    <tableColumn id="13" xr3:uid="{E3E8CC1C-2048-4C68-8C73-9C23BAF8E279}" uniqueName="13" name="PreviousRun1" queryTableFieldId="13" dataDxfId="4"/>
+    <tableColumn id="14" xr3:uid="{AE7BAA4D-E3D2-4285-BE3D-A239D2F62EF4}" uniqueName="14" name="PreviousRun2" queryTableFieldId="14" dataDxfId="3"/>
+    <tableColumn id="15" xr3:uid="{301D8E6F-5DBC-42B5-8017-5B59010563CF}" uniqueName="15" name="PreviousRun3" queryTableFieldId="15" dataDxfId="2"/>
+    <tableColumn id="16" xr3:uid="{D035B195-9C84-45C1-B235-F06BB2F9A3DF}" uniqueName="16" name="PreviousRun4" queryTableFieldId="16" dataDxfId="1"/>
+    <tableColumn id="17" xr3:uid="{7D5B7342-1370-4300-B6E6-1A36CD80694B}" uniqueName="17" name="PreviousRun5" queryTableFieldId="17" dataDxfId="0"/>
+    <tableColumn id="18" xr3:uid="{A389CD95-6B82-4DB3-AED0-52BE817E75F0}" uniqueName="18" name="PreviousRun6" queryTableFieldId="18" dataDxfId="16"/>
+    <tableColumn id="19" xr3:uid="{9B99B349-B48C-49EC-883C-00BE7E54D37D}" uniqueName="19" name="Volume0Name" queryTableFieldId="19" dataDxfId="15"/>
+    <tableColumn id="20" xr3:uid="{DA95DC40-6B11-4BC8-A7FC-48424A1DF5ED}" uniqueName="20" name="Volume0Serial" queryTableFieldId="20" dataDxfId="14"/>
+    <tableColumn id="21" xr3:uid="{6905E521-84A5-4DEA-A4D9-9767759B6F0F}" uniqueName="21" name="Volume0Created" queryTableFieldId="21" dataDxfId="13"/>
+    <tableColumn id="22" xr3:uid="{BC82989A-24DF-4EDB-80D2-024D565C2C30}" uniqueName="22" name="Volume1Name" queryTableFieldId="22" dataDxfId="12"/>
+    <tableColumn id="23" xr3:uid="{1EF047D8-22C4-40DB-A5C8-16C025AC50EF}" uniqueName="23" name="Volume1Serial" queryTableFieldId="23" dataDxfId="11"/>
+    <tableColumn id="24" xr3:uid="{BDC1B3CA-3F53-4B10-8636-BFE8CAEDDD90}" uniqueName="24" name="Volume1Created" queryTableFieldId="24" dataDxfId="10"/>
+    <tableColumn id="25" xr3:uid="{02AC2FC1-9EAF-49E2-97EB-698A7B7C06C4}" uniqueName="25" name="Directories" queryTableFieldId="25" dataDxfId="9"/>
+    <tableColumn id="26" xr3:uid="{E668B0CD-9181-44EB-8C2E-BC0D72847997}" uniqueName="26" name="FilesLoaded" queryTableFieldId="26" dataDxfId="8"/>
     <tableColumn id="27" xr3:uid="{DFFF69A4-DD76-4971-A1D3-206E5E9738B2}" uniqueName="27" name="ParsingError" queryTableFieldId="27"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -388,11 +351,11 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6E6CC3F6-3D58-412A-8AC5-878EAF5D0424}" name="_20260429005736_PECmd_Output_Timeline" displayName="_20260429005736_PECmd_Output_Timeline" ref="A1:B9" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:B9" xr:uid="{33EDF663-A7DD-4566-A4A1-64E5A324873D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6E6CC3F6-3D58-412A-8AC5-878EAF5D0424}" name="_20260429005736_PECmd_Output_Timeline" displayName="_20260429005736_PECmd_Output_Timeline" ref="A1:B8" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:B8" xr:uid="{33EDF663-A7DD-4566-A4A1-64E5A324873D}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{366635B8-E43A-4219-B002-8C38FC2EBD60}" uniqueName="1" name="RunTime" queryTableFieldId="1" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{DB531C46-1148-4A19-81AC-D4E407F58B92}" uniqueName="2" name="ExecutableName" queryTableFieldId="2" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{366635B8-E43A-4219-B002-8C38FC2EBD60}" uniqueName="1" name="RunTime" queryTableFieldId="1" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{DB531C46-1148-4A19-81AC-D4E407F58B92}" uniqueName="2" name="ExecutableName" queryTableFieldId="2" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -715,32 +678,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10BCE2CC-6B44-4745-BF35-D6AC8DC275A9}">
-  <dimension ref="A1:AA2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:V2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="59.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="18" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="34.6640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="255.77734375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="13" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="34.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="255.83203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -807,102 +765,70 @@
       <c r="V1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2">
+        <v>346930</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2">
+        <v>7</v>
+      </c>
+      <c r="F2" s="1">
+        <v>46136.773715277777</v>
+      </c>
+      <c r="G2" s="1">
+        <v>46136.772800925923</v>
+      </c>
+      <c r="H2" s="1">
+        <v>46136.769178240742</v>
+      </c>
+      <c r="I2" s="1">
+        <v>46136.768599537034</v>
+      </c>
+      <c r="J2" s="1">
+        <v>46136.767766203702</v>
+      </c>
+      <c r="K2" s="1">
+        <v>46136.766944444447</v>
+      </c>
+      <c r="L2" s="1">
+        <v>46136.766956018517</v>
+      </c>
+      <c r="M2" s="1"/>
+      <c r="N2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P2" s="1">
+        <v>46133.084305555552</v>
+      </c>
+      <c r="Q2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="R2" t="s">
+        <v>22</v>
+      </c>
+      <c r="S2" t="s">
+        <v>22</v>
+      </c>
+      <c r="T2" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="1">
-        <v>46140.404652777775</v>
-      </c>
-      <c r="D2" s="1">
-        <v>46140.552534722221</v>
-      </c>
-      <c r="E2" s="1">
-        <v>46141.039988425924</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="U2" t="s">
         <v>29</v>
       </c>
-      <c r="G2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H2">
-        <v>346930</v>
-      </c>
-      <c r="I2" t="s">
-        <v>31</v>
-      </c>
-      <c r="J2">
-        <v>9</v>
-      </c>
-      <c r="K2" s="1">
-        <v>46136.945162037038</v>
-      </c>
-      <c r="L2" s="1">
-        <v>46136.773715277777</v>
-      </c>
-      <c r="M2" s="1">
-        <v>46136.772800925923</v>
-      </c>
-      <c r="N2" s="1">
-        <v>46136.769178240742</v>
-      </c>
-      <c r="O2" s="1">
-        <v>46136.768599537034</v>
-      </c>
-      <c r="P2" s="1">
-        <v>46136.767766203702</v>
-      </c>
-      <c r="Q2" s="1">
-        <v>46136.766944444447</v>
-      </c>
-      <c r="R2" s="1">
-        <v>46136.766956018517</v>
-      </c>
-      <c r="S2" t="s">
-        <v>32</v>
-      </c>
-      <c r="T2" t="s">
-        <v>33</v>
-      </c>
-      <c r="U2" s="1">
-        <v>46133.084305555552</v>
-      </c>
-      <c r="V2" t="s">
-        <v>27</v>
-      </c>
-      <c r="W2" t="s">
-        <v>27</v>
-      </c>
-      <c r="X2" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>34</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA2" t="b">
+      <c r="V2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -916,83 +842,75 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2DA04DF-7A52-40A1-B3B8-4475B203625A}">
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="104.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
-        <v>46136.945162037038</v>
+        <v>46136.773715277777</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
-        <v>46136.773715277777</v>
+        <v>46136.772800925923</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
-        <v>46136.772800925923</v>
+        <v>46136.769178240742</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
-        <v>46136.769178240742</v>
+        <v>46136.768599537034</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
-        <v>46136.768599537034</v>
+        <v>46136.767766203702</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
-        <v>46136.767766203702</v>
+        <v>46136.766944444447</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
-        <v>46136.766944444447</v>
+        <v>46136.766956018517</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
-        <v>46136.766956018517</v>
-      </c>
-      <c r="B9" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
